--- a/src/main/resources/static/de_thi_mau.xlsx
+++ b/src/main/resources/static/de_thi_mau.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="De thi mau" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="De thi mau 30 cau" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -456,10 +456,10 @@
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="31" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
@@ -527,44 +527,52 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SINGLE</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr"/>
+          <t>MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI) is rapidly transforming modern society. From healthcare diagnosis to autonomous driving, machine learning algorithms are proving to be highly efficient at tasks that once required human intelligence. However, this technological leap raises significant ethical concerns. Data privacy issues, bias in algorithms, and job displacement are key hurdles. Experts emphasize that while AI offers immense potential, regulatory frameworks must be established to ensure it serves the common good and minimizes societal harm.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
+        </is>
+      </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Căn bậc hai của 64 là bao nhiêu?</t>
+          <t>What is the main theme of the passage about AI?</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>The complete replacement of human workforce by machines</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>The rapid progress of AI and its associated ethical hurdles</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>A detailed history of computer science developments</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>How autonomous driving systems are constructed</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Căn bậc hai của 64 bằng 8 vì 8 * 8 = 64.</t>
+          <t>Đoạn văn thảo luận về sự phát triển nhanh chóng của AI đi kèm các lo ngại đạo đức.</t>
         </is>
       </c>
     </row>
@@ -579,47 +587,47 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>The search for clean and sustainable energy sources has led scientists to explore various options. Solar energy, which harnesses power from the sun, has emerged as one of the most promising renewable sources. It is clean, abundant, and available in most parts of the world. However, the high initial cost of solar panels and their dependency on sunlight remain key challenges that researchers are working to overcome.</t>
+          <t>Artificial Intelligence (AI) is rapidly transforming modern society. From healthcare diagnosis to autonomous driving, machine learning algorithms are proving to be highly efficient at tasks that once required human intelligence. However, this technological leap raises significant ethical concerns. Data privacy issues, bias in algorithms, and job displacement are key hurdles. Experts emphasize that while AI offers immense potential, regulatory frameworks must be established to ensure it serves the common good and minimizes societal harm.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Đọc đoạn văn và chọn đáp án chính xác nhất.</t>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>What is the main topic of the passage?</t>
+          <t>According to the passage, which of the following is NOT an ethical issue of AI?</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Fossil fuels</t>
+          <t>Data privacy concerns</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Renewable energy source (Solar energy)</t>
+          <t>Job displacement</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Nuclear power development</t>
+          <t>Algorithmic bias</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Geothermal energy challenges</t>
+          <t>High energy consumption of data centers</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Đoạn văn chủ yếu giới thiệu về năng lượng mặt trời như một nguồn năng lượng tái tạo.</t>
+          <t>Đoạn văn nhắc tới privacy, bias, job displacement nhưng không nói về năng lượng tiêu thụ.</t>
         </is>
       </c>
     </row>
@@ -634,47 +642,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>The search for clean and sustainable energy sources has led scientists to explore various options. Solar energy, which harnesses power from the sun, has emerged as one of the most promising renewable sources. It is clean, abundant, and available in most parts of the world. However, the high initial cost of solar panels and their dependency on sunlight remain key challenges that researchers are working to overcome.</t>
+          <t>Artificial Intelligence (AI) is rapidly transforming modern society. From healthcare diagnosis to autonomous driving, machine learning algorithms are proving to be highly efficient at tasks that once required human intelligence. However, this technological leap raises significant ethical concerns. Data privacy issues, bias in algorithms, and job displacement are key hurdles. Experts emphasize that while AI offers immense potential, regulatory frameworks must be established to ensure it serves the common good and minimizes societal harm.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Đọc đoạn văn và chọn đáp án chính xác nhất.</t>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>According to the passage, what is one of the key challenges of solar energy?</t>
+          <t>The word 'leap' in the passage is closest in meaning to __________.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>It produces toxic waste</t>
+          <t>fall</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>It is not clean</t>
+          <t>jump</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>High initial cost of solar panels</t>
+          <t>barrier</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>It is not abundant</t>
+          <t>decrease</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Dòng cuối đoạn văn có ghi 'high initial cost of solar panels... remain key challenges'.</t>
+          <t>Leap có nghĩa là bước nhảy vọt, đồng nghĩa với jump.</t>
         </is>
       </c>
     </row>
@@ -684,44 +692,1322 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI) is rapidly transforming modern society. From healthcare diagnosis to autonomous driving, machine learning algorithms are proving to be highly efficient at tasks that once required human intelligence. However, this technological leap raises significant ethical concerns. Data privacy issues, bias in algorithms, and job displacement are key hurdles. Experts emphasize that while AI offers immense potential, regulatory frameworks must be established to ensure it serves the common good and minimizes societal harm.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>What do experts suggest to ensure AI is beneficial to society?</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Banning all machine learning research completely</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Allowing companies to self-regulate without government control</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Establishing strong regulatory frameworks</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Replacing all healthcare workers with AI tools</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Dòng cuối đoạn văn có ghi 'regulatory frameworks must be established'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI) is rapidly transforming modern society. From healthcare diagnosis to autonomous driving, machine learning algorithms are proving to be highly efficient at tasks that once required human intelligence. However, this technological leap raises significant ethical concerns. Data privacy issues, bias in algorithms, and job displacement are key hurdles. Experts emphasize that while AI offers immense potential, regulatory frameworks must be established to ensure it serves the common good and minimizes societal harm.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>It can be inferred from the passage that AI ___________.</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Is already completely safe and requires no human oversight</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Has proven to be highly efficient in healthcare and driving</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Is only useful for simple repetitive calculating tasks</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Will not affect the future job market at all</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Đoạn đầu có ghi 'From healthcare diagnosis to autonomous driving... highly efficient'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>SINGLE</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Thủ đô của nước Cộng hòa Xã hội Chủ nghĩa Việt Nam là thành phố nào?</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Năm 1945, sự kiện nào đánh dấu cuộc Cách mạng tháng Tám thành công ở Việt Nam?</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Chiến thắng Điện Biên Phủ</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Chủ tịch Hồ Chí Minh đọc Tuyên ngôn Độc lập ngày 2/9</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Hiệp định Giơ-ne-vơ được ký kết</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Thành lập Mặt trận Việt Minh</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Ngày 2/9/1945 Chủ tịch Hồ Chí Minh đọc Tuyên ngôn Độc lập khai sinh nước VNDCCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Trận chung kết chiến dịch Điện Biên Phủ diễn ra vào năm nào?</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>1954</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Chiến thắng Điện Biên Phủ diễn ra vào ngày 7/5/1954.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Hành tinh nào gần Mặt Trời nhất trong Hệ Mặt Trời?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Sao Kim</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Sao Hỏa</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Sao Thủy</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Trái Đất</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Sao Thủy (Mercury) là hành tinh nằm gần Mặt Trời nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr"/>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Chất nào chiếm tỷ lệ phần trăm thể tích lớn nhất trong không khí?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Khí Oxi</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Khí Nitơ</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Khí Cacbonic</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Khí Heli</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Khí Nitơ chiếm khoảng 78% thể tích không khí khô.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Công thức hóa học của muối ăn thông thường là gì?</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>HCl</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>NaOH</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>NaCl</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>NaHCO3</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Muối ăn có công thức hóa học là Natri Clorua (NaCl).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Ai là tác giả của tác phẩm văn học nổi tiếng 'Truyện Kiều'?</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Trãi</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Du</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Hồ Xuân Hương</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Đoàn Thị Điểm</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Du là tác giả vĩ đại của Truyện Kiều.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Số nguyên tố nhỏ nhất là số nào?</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Số 2 là số nguyên tố nhỏ nhất và cũng là số nguyên tố chẵn duy nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Tỉnh nào có diện tích lớn nhất Việt Nam?</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Thanh Hóa</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Lâm Đồng</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Sơn La</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>Nghệ An</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Nghệ An là tỉnh có diện tích lớn nhất Việt Nam (khoảng 16,493 km2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Cơ quan nào trong cơ thể con người chịu trách nhiệm lọc máu và tạo ra nước tiểu?</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Gan</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Tim</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Thận</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Phổi</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Thận chịu trách nhiệm lọc máu và bài tiết nước tiểu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Trong vật lý, đại lượng nào đặc trưng cho mức độ nhanh chậm của chuyển động?</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Gia tốc</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Vận tốc</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Quãng đường</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>Lực</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Vận tốc đặc trưng cho sự nhanh chậm của chuyển động.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Global warming and climate change pose unprecedented threats to Earth's ecosystems. Rising temperatures have caused polar ice caps to melt, leading to rising sea levels that threaten coastal cities worldwide. Extreme weather events, such as severe droughts and catastrophic storms, have become more frequent and intense. Transitioning from fossil fuels to renewable energy sources like wind and solar power is critical to reducing carbon emissions. Individual actions combined with international agreements like the Paris Accord are essential steps in combating this global crisis.</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>What is causing polar ice caps to melt, according to the passage?</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Sudden changes in Earth's gravitational pull</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Rising temperatures due to global warming</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>An increase in wind power generation</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Decreased solar radiation</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Đoạn văn nêu rõ 'Rising temperatures have caused polar ice caps to melt'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Global warming and climate change pose unprecedented threats to Earth's ecosystems. Rising temperatures have caused polar ice caps to melt, leading to rising sea levels that threaten coastal cities worldwide. Extreme weather events, such as severe droughts and catastrophic storms, have become more frequent and intense. Transitioning from fossil fuels to renewable energy sources like wind and solar power is critical to reducing carbon emissions. Individual actions combined with international agreements like the Paris Accord are essential steps in combating this global crisis.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Which extreme weather events are mentioned as becoming more frequent?</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Blizzards and volcanic eruptions</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Earthquakes and tsunamis</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Severe droughts and catastrophic storms</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Sandstorms and acid rain</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Đoạn văn nêu 'extreme weather events, such as severe droughts and catastrophic storms'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Global warming and climate change pose unprecedented threats to Earth's ecosystems. Rising temperatures have caused polar ice caps to melt, leading to rising sea levels that threaten coastal cities worldwide. Extreme weather events, such as severe droughts and catastrophic storms, have become more frequent and intense. Transitioning from fossil fuels to renewable energy sources like wind and solar power is critical to reducing carbon emissions. Individual actions combined with international agreements like the Paris Accord are essential steps in combating this global crisis.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>What is highlighted as a critical step to reduce carbon emissions?</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Increasing fossil fuel usage</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Transitioning to renewable energy like wind and solar power</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Building larger cities along the coasts</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Relying solely on local individual actions</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Đoạn văn viết 'Transitioning from fossil fuels to renewable energy... is critical'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Global warming and climate change pose unprecedented threats to Earth's ecosystems. Rising temperatures have caused polar ice caps to melt, leading to rising sea levels that threaten coastal cities worldwide. Extreme weather events, such as severe droughts and catastrophic storms, have become more frequent and intense. Transitioning from fossil fuels to renewable energy sources like wind and solar power is critical to reducing carbon emissions. Individual actions combined with international agreements like the Paris Accord are essential steps in combating this global crisis.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Which international agreement is cited in the passage?</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>The Kyoto Protocol</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>The Paris Accord</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>The Geneva Convention</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>The Montreal Protocol</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Đoạn văn có nhắc tới 'Paris Accord'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>MULTIPLE</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Global warming and climate change pose unprecedented threats to Earth's ecosystems. Rising temperatures have caused polar ice caps to melt, leading to rising sea levels that threaten coastal cities worldwide. Extreme weather events, such as severe droughts and catastrophic storms, have become more frequent and intense. Transitioning from fossil fuels to renewable energy sources like wind and solar power is critical to reducing carbon emissions. Individual actions combined with international agreements like the Paris Accord are essential steps in combating this global crisis.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Đọc đoạn văn và chọn phương án trả lời chính xác nhất.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>It can be concluded from the text that climate change ___________.</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Only affects polar bears and cold regions</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Requires both individual efforts and international cooperation</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Will resolve itself naturally in a few years</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Has no connection with rising ocean levels</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Câu cuối có ghi 'Individual actions combined with international agreements... are essential'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Loại sóng nào được sử dụng trong lò vi sóng để hâm nóng thức ăn?</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Sóng hồng ngoại</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Sóng vi ba</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Tia tử ngoại</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>Tia X</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Lò vi sóng sử dụng sóng vi ba (microwaves) để hâm nóng thức ăn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Nước Việt Nam nằm trong múi giờ thứ mấy (GMT/UTC)?</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Việt Nam nằm ở múi giờ GMT+7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Bộ phận nào của thực vật thực hiện quá trình quang hợp chính?</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Rễ</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Thân</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Lá</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>Hoa</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Lá cây chứa diệp lục chịu trách nhiệm chính cho quang hợp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Tập hợp tất cả các giá trị của x thỏa mãn x^2 = 9 là:</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>{3}</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>{-3}</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>{3, -3}</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>{9, -9}</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Phương trình x^2 = 9 có hai nghiệm là x = 3 và x = -3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr"/>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Tác phẩm 'Tắt đèn' là của nhà văn nào?</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Nam Cao</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Ngô Tất Tố</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Vũ Trọng Phụng</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Nguyễn Công Hoan</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Tác phẩm 'Tắt đèn' nổi tiếng được viết bởi nhà văn Ngô Tất Tố.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr"/>
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Ai là người đầu tiên đặt chân lên Mặt Trăng?</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Yuri Gagarin</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Neil Armstrong</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Buzz Aldrin</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Michael Collins</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Neil Armstrong là người đầu tiên đặt chân lên Mặt Trăng vào năm 1969.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Quốc gia nào có diện tích lớn nhất thế giới?</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Hoa Kỳ</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Trung Quốc</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Nga</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Liên bang Nga là quốc gia có diện tích lớn nhất thế giới.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Loại axit nào có sẵn trong dạ dày con người để hỗ trợ tiêu hóa thức ăn?</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Axit Sunfuric (H2SO4)</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Axit Clohidric (HCl)</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Axit Axetic (CH3COOH)</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Axit Nitric (HNO3)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Dạ dày tiết ra Axit Clohidric (HCl) để tiêu hóa thức ăn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Giải bóng đá vô địch thế giới (World Cup) được tổ chức định kỳ mấy năm một lần?</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>2 năm</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>3 năm</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>4 năm</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>5 năm</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>World Cup được tổ chức định kỳ 4 năm một lần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SINGLE</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr"/>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Thành phố nào là trung tâm kinh tế lớn nhất miền Nam Việt Nam?</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Cần Thơ</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Đà Nẵng</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Bình Dương</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Thành phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Đà Nẵng</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Hải Phòng</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Hà Nội</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Hà Nội là thủ đô của Việt Nam.</t>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Thành phố Hồ Chí Minh là trung tâm kinh tế lớn nhất miền Nam và cả nước.</t>
         </is>
       </c>
     </row>
